--- a/Project5518_D. Cusco(2025).xlsx
+++ b/Project5518_D. Cusco(2025).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\neotrans\inst\matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978AD85C-97B2-4579-A60C-164389D99ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B580BE81-9619-4E63-BF6D-BB54A847D6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF8048CC-CEC8-4454-8E49-5C7746D4C3A2}"/>
   </bookViews>

--- a/Project5518_D. Cusco(2025).xlsx
+++ b/Project5518_D. Cusco(2025).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\neotrans\inst\matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B580BE81-9619-4E63-BF6D-BB54A847D6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DB6DA0-82AD-4EA8-85C8-14841BE6C296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF8048CC-CEC8-4454-8E49-5C7746D4C3A2}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="87">
   <si>
     <t>Charlabels</t>
   </si>
@@ -803,6 +803,9 @@
       <c r="B2" t="s">
         <v>83</v>
       </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -1426,6 +1429,9 @@
       </c>
       <c r="B47" t="s">
         <v>86</v>
+      </c>
+      <c r="D47" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
